--- a/DataTables/Datas/#Entity.xlsx
+++ b/DataTables/Datas/#Entity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -74,15 +74,6 @@
   </si>
   <si>
     <t>敌人推进器</t>
-  </si>
-  <si>
-    <t>DefaultWeapon</t>
-  </si>
-  <si>
-    <t>玩家武器</t>
-  </si>
-  <si>
-    <t>敌人武器</t>
   </si>
   <si>
     <t>DefaultArmor</t>
@@ -1110,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
@@ -1216,7 +1207,7 @@
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1228,7 +1219,7 @@
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="2">
-        <v>30001</v>
+        <v>40001</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
@@ -1240,7 +1231,7 @@
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="2">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>23</v>
@@ -1252,111 +1243,87 @@
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="2">
-        <v>40001</v>
+        <v>50001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="2">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="2">
-        <v>50001</v>
+        <v>60001</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="2">
-        <v>60000</v>
+        <v>60002</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="2">
-        <v>60001</v>
+        <v>70000</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="2">
-        <v>60002</v>
+        <v>70001</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="2">
-        <v>70000</v>
+        <v>70002</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="2">
-        <v>70001</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="2">
-        <v>70002</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Datas/#Entity.xlsx
+++ b/DataTables/Datas/#Entity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -64,6 +64,54 @@
     <t>敌人战机</t>
   </si>
   <si>
+    <t>PlayerBolt</t>
+  </si>
+  <si>
+    <t>玩家子弹</t>
+  </si>
+  <si>
+    <t>EnemyBolt</t>
+  </si>
+  <si>
+    <t>敌人子弹</t>
+  </si>
+  <si>
+    <t>Asteroid01</t>
+  </si>
+  <si>
+    <t>小行星01</t>
+  </si>
+  <si>
+    <t>Asteroid02</t>
+  </si>
+  <si>
+    <t>小行星02</t>
+  </si>
+  <si>
+    <t>Asteroid03</t>
+  </si>
+  <si>
+    <t>小行星03</t>
+  </si>
+  <si>
+    <t>PlayerExplosion</t>
+  </si>
+  <si>
+    <t>玩家死亡特效</t>
+  </si>
+  <si>
+    <t>EnemyExplosion</t>
+  </si>
+  <si>
+    <t>敌人死亡特效</t>
+  </si>
+  <si>
+    <t>AsteroidExplosion</t>
+  </si>
+  <si>
+    <t>小行星死亡特效</t>
+  </si>
+  <si>
     <t>PlayerEngine</t>
   </si>
   <si>
@@ -74,63 +122,6 @@
   </si>
   <si>
     <t>敌人推进器</t>
-  </si>
-  <si>
-    <t>DefaultArmor</t>
-  </si>
-  <si>
-    <t>玩家装甲</t>
-  </si>
-  <si>
-    <t>敌人装甲</t>
-  </si>
-  <si>
-    <t>PlayerBolt</t>
-  </si>
-  <si>
-    <t>玩家子弹</t>
-  </si>
-  <si>
-    <t>EnemyBolt</t>
-  </si>
-  <si>
-    <t>敌人子弹</t>
-  </si>
-  <si>
-    <t>Asteroid01</t>
-  </si>
-  <si>
-    <t>小行星01</t>
-  </si>
-  <si>
-    <t>Asteroid02</t>
-  </si>
-  <si>
-    <t>小行星02</t>
-  </si>
-  <si>
-    <t>Asteroid03</t>
-  </si>
-  <si>
-    <t>小行星03</t>
-  </si>
-  <si>
-    <t>PlayerExplosion</t>
-  </si>
-  <si>
-    <t>玩家死亡特效</t>
-  </si>
-  <si>
-    <t>EnemyExplosion</t>
-  </si>
-  <si>
-    <t>敌人死亡特效</t>
-  </si>
-  <si>
-    <t>AsteroidExplosion</t>
-  </si>
-  <si>
-    <t>小行星死亡特效</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1092,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
@@ -1183,7 +1174,7 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="2">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>16</v>
@@ -1195,7 +1186,7 @@
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="2">
-        <v>20001</v>
+        <v>50001</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>18</v>
@@ -1207,7 +1198,7 @@
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="2">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1219,111 +1210,87 @@
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="2">
-        <v>40001</v>
+        <v>60001</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="2">
-        <v>50000</v>
+        <v>60002</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="2">
-        <v>50001</v>
+        <v>70000</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="2">
-        <v>60000</v>
+        <v>70001</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="2">
-        <v>60001</v>
+        <v>70002</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="2">
-        <v>60002</v>
+        <v>70003</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="2">
-        <v>70000</v>
+        <v>70004</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="2">
-        <v>70001</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="2">
-        <v>70002</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Datas/#Entity.xlsx
+++ b/DataTables/Datas/#Entity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>敌人推进器</t>
+  </si>
+  <si>
+    <t>Hero_101001</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
@@ -1292,6 +1295,14 @@
       </c>
       <c r="E16" s="2"/>
     </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <v>101001</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/DataTables/Datas/#Entity.xlsx
+++ b/DataTables/Datas/#Entity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>Hero_101001</t>
+  </si>
+  <si>
+    <t>Enemy_201001</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1098,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
@@ -1303,6 +1306,14 @@
         <v>36</v>
       </c>
     </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>201001</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/DataTables/Datas/#Entity.xlsx
+++ b/DataTables/Datas/#Entity.xlsx
@@ -1,306 +1,182 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>实体id</t>
-  </si>
-  <si>
-    <t>资源名称</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>PlayerShip</t>
-  </si>
-  <si>
-    <t>玩家战机</t>
-  </si>
-  <si>
-    <t>EnemyShip</t>
-  </si>
-  <si>
-    <t>敌人战机</t>
-  </si>
-  <si>
-    <t>PlayerBolt</t>
-  </si>
-  <si>
-    <t>玩家子弹</t>
-  </si>
-  <si>
-    <t>EnemyBolt</t>
-  </si>
-  <si>
-    <t>敌人子弹</t>
-  </si>
-  <si>
-    <t>Asteroid01</t>
-  </si>
-  <si>
-    <t>小行星01</t>
-  </si>
-  <si>
-    <t>Asteroid02</t>
-  </si>
-  <si>
-    <t>小行星02</t>
-  </si>
-  <si>
-    <t>Asteroid03</t>
-  </si>
-  <si>
-    <t>小行星03</t>
-  </si>
-  <si>
-    <t>PlayerExplosion</t>
-  </si>
-  <si>
-    <t>玩家死亡特效</t>
-  </si>
-  <si>
-    <t>EnemyExplosion</t>
-  </si>
-  <si>
-    <t>敌人死亡特效</t>
-  </si>
-  <si>
-    <t>AsteroidExplosion</t>
-  </si>
-  <si>
-    <t>小行星死亡特效</t>
-  </si>
-  <si>
-    <t>PlayerEngine</t>
-  </si>
-  <si>
-    <t>玩家推进器</t>
-  </si>
-  <si>
-    <t>EnemyEngine</t>
-  </si>
-  <si>
-    <t>敌人推进器</t>
-  </si>
-  <si>
-    <t>Hero_101001</t>
-  </si>
-  <si>
-    <t>Enemy_201001</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -621,164 +497,165 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -832,11 +709,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1096,226 +1036,366 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
-    <col min="2" max="2" width="11.1607142857143" customWidth="1"/>
-    <col min="3" max="3" width="23.8035714285714" customWidth="1"/>
-    <col min="4" max="4" width="21.7232142857143" customWidth="1"/>
+    <col width="8.21428571428571" customWidth="1" style="3" min="1" max="1"/>
+    <col width="11.1607142857143" customWidth="1" style="3" min="2" max="2"/>
+    <col width="23.8035714285714" customWidth="1" style="3" min="3" max="3"/>
+    <col width="21.7232142857143" customWidth="1" style="3" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>实体id</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>资源名称</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="2">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>PlayerShip</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>玩家战机</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n">
         <v>10001</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="2">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EnemyShip</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>敌人战机</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="n">
         <v>50000</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="2">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>PlayerBolt</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>玩家子弹</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="n">
         <v>50001</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="2">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EnemyBolt</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>敌人子弹</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="n">
         <v>60000</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="2">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Asteroid01</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>小行星01</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="n">
         <v>60001</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="2">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Asteroid02</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>小行星02</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="n">
         <v>60002</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="2">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Asteroid03</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>小行星03</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="n">
         <v>70000</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="2">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>PlayerExplosion</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>玩家死亡特效</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="n">
         <v>70001</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="B14" s="2">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EnemyExplosion</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>敌人死亡特效</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="n">
         <v>70002</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="2">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>AsteroidExplosion</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>小行星死亡特效</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="n">
         <v>70003</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="2:5">
-      <c r="B16" s="2">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PlayerEngine</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>玩家推进器</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="n">
         <v>70004</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EnemyEngine</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>敌人推进器</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="n">
         <v>101001</v>
       </c>
-      <c r="C17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Hero_101001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="n">
         <v>201001</v>
       </c>
-      <c r="C18" t="s">
-        <v>37</v>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Enemy_201001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Bolt_500001</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>弹幕</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="n">
+        <v>701001</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Effect_701001</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>弹幕命中特效</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>300001</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gem_300001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>经验宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>500002</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DamageText_500002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>伤害飘字</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>